--- a/worklog/v2.2.3/s10/v4/pjm/test/ods_progress_measure_v2.xlsx
+++ b/worklog/v2.2.3/s10/v4/pjm/test/ods_progress_measure_v2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="进度跟进措施表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ods_progress_measure_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,174 +413,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>分系统/分任务</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>节点任务及目标</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>节点计划时间</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>节点计划周数</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>完成情况</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>跟进措施类别</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>跟进措施题目</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>跟进人</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>主送</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>抄送</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>跟进时间</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>跟进周数</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>闭环状态</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>最终闭环时间</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>最终闭环周数</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>闭环交付物类别</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>闭环交付物</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>主要风险内容</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新时间</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新周数</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>填写人</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>subsystem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>node_task</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>plan_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>plan_week</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>completion_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>measure_category</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>measure_title</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>follow_up_person</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>main_recipient</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cc_recipient</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>follow_up_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>follow_up_week</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>closure_status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>final_closure_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>final_closure_week</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>closure_deliverable_type</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>closure_deliverable</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>risk_content</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>last_update_time</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>last_update_week</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>filled_by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>控制分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>控制软件初样验证</t>
+          <t>综合统筹平台详细设计评审</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>28</v>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -601,36 +566,38 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>重要跟进</t>
+          <t>常规跟进</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>初样软件超期归因及闭环措施</t>
+          <t>综合统筹平台详细设计评审闭环跟进</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>刘工</t>
+          <t>王工</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>赵总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>张总</t>
+          <t>李所</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>29</v>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -639,11 +606,13 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>29</v>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -652,56 +621,60 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>软件归因报告;回归测试记录</t>
+          <t>详细设计报告;闭环纪要</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>软件bug修复延期10天</t>
+          <t>综合统筹平台接口收敛偏慢</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>29</v>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>评审意见梳理完整</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>刘工</t>
+          <t>王工</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>热试车</t>
+          <t>飞控执行机构联调准备</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>48</v>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -715,17 +688,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>热试车异常振动归零跟进</t>
+          <t>飞控执行机构联调准备闭环跟进</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -735,73 +708,78 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>49</v>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>排查分析报告</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>异常振动排查</t>
+          <t>飞控执行机构联调输入条件变更</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>52</v>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>持续跟进</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>动力分系统</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>制导仿真验证</t>
+          <t>姿轨动力系统详细设计评审</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>28</v>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期已完成未变更</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -811,17 +789,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>仿真参数修正跟进</t>
+          <t>姿轨动力系统详细设计评审闭环跟进</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -831,11 +809,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>26</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -844,11 +824,13 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>29</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -857,80 +839,84 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>仿真修正报告</t>
+          <t>详细设计报告;闭环纪要</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>仿真偏差3%</t>
+          <t>姿轨动力系统接口收敛偏慢</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>29</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>遥测天线设计</t>
+          <t>惯导制导系统联调准备</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>19</v>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>超期已完成已变更</t>
+          <t>超期未完成已变更</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>常规跟进</t>
+          <t>重大跟进</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>天线方向图修正跟进</t>
+          <t>惯导制导系统联调准备闭环跟进</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>徐工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>郑总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,86 +926,78 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>20</v>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>已闭环</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>天线修正报告</t>
-        </is>
-      </c>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>方向图偏离</t>
+          <t>惯导制导系统联调输入条件变更</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>22</v>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>徐工</t>
+          <t>林工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>电源分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>蓄电池组研制</t>
+          <t>实时软件平台详细设计评审</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>23</v>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成未变更</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1029,17 +1007,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>蓄电池循环性能跟进</t>
+          <t>实时软件平台详细设计评审闭环跟进</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1049,11 +1027,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>23</v>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1062,11 +1042,13 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>33</v>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1075,37 +1057,39 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>循环测试报告</t>
+          <t>详细设计报告;闭环纪要</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>循环寿命不足</t>
+          <t>实时软件平台接口收敛偏慢</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>33</v>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,35 +1099,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>结构件试制</t>
+          <t>复合结构组件联调准备</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>39</v>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期未完成已变更</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>常规跟进</t>
+          <t>重大跟进</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>结构件试制工艺跟进</t>
+          <t>复合结构组件联调准备闭环跟进</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>余工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1158,93 +1144,98 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>38</v>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>试制周报</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>试制工艺待打通</t>
+          <t>复合结构组件联调输入条件变更</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>39</v>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>持续跟进</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>余工</t>
+          <t>周工</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>测控分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>测控主机研制</t>
+          <t>高可靠电源系统详细设计评审</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>25</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>超期已完成已变更</t>
+          <t>超期已完成未变更</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>重要跟进</t>
+          <t>常规跟进</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>测控主机元器件替换跟进</t>
+          <t>高可靠电源系统详细设计评审闭环跟进</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1254,11 +1245,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>25</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1267,11 +1260,13 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>26</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1280,60 +1275,64 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>替换试验报告</t>
+          <t>详细设计报告;闭环纪要</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>元器件批次问题</t>
+          <t>高可靠电源系统接口收敛偏慢</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>26</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>已闭环</t>
+          <t>与关键节点状态同步</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>可靠性试验</t>
+          <t>电子载荷组件联调准备</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>50</v>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>不正常待变更</t>
+          <t>超期未完成已变更</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1343,61 +1342,282 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>可靠性归零技术跟进</t>
+          <t>电子载荷组件联调准备闭环跟进</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>郑总</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>电子载荷组件联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>与关键节点状态同步</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>测控分系统</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>测控链路系统详细设计评审</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>超期已完成未变更</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>常规跟进</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>测控链路系统详细设计评审闭环跟进</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>已闭环</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>详细设计报告;闭环纪要</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>测控链路系统接口收敛偏慢</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>与关键节点状态同步</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>试验分系统</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台联调准备</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2027-04-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>超期未完成已变更</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>重大跟进</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台联调准备闭环跟进</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>柳工</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>曹总</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>李所</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-12-05</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>49</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2027-04-19</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>失效分析报告</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>局部可靠性不达标</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>51</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>持续跟进</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>环境试验保障平台联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2027-04-19</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>与关键节点状态同步</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>柳工</t>
         </is>
